--- a/runs/RELX/2026-10-14/bear/scratch/b_acq_27/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_acq_27/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1830.335374499225</v>
+        <v>1882.208737468233</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600960394000001</v>
+        <v>0.089224054516</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9962.534138312603</v>
+        <v>10113.7502542251</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>37880.3647832059</v>
+        <v>41593.51174104817</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>25075.49608778312</v>
+        <v>28313.79494258443</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>35038.03022609573</v>
+        <v>38427.54519680953</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>28041.03022609573</v>
+        <v>31430.54519680953</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>27009.8188093476</v>
+        <v>30482.54212802797</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>15.48945983694392</v>
+        <v>17.48098035580434</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1548.945983694392</v>
+        <v>1748.098035580434</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4410155237</v>
+        <v>-0.369145422</v>
       </c>
     </row>
   </sheetData>
